--- a/data_extactor/batch/351_400.xlsx
+++ b/data_extactor/batch/351_400.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sarbazi\code\sarbazi\data_extactor\batch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5539FB0C-9FD6-4BFE-9E61-4070A55AA324}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{609D6BFB-03C8-4E2C-A48A-B4CD63C9C935}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="495">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="540">
   <si>
     <t>25-3011.00</t>
   </si>
@@ -1510,6 +1510,141 @@
   </si>
   <si>
     <t>Collaborate with other writers on specific projects. | Conduct research and interviews to determine which of a product's selling features should be promoted. | Conduct research to obtain factual information and authentic detail, using sources such as newspaper accounts, diaries, and interviews. | Consult with sales, media and marketing representatives to obtain information on product or service and discuss style and length of advertising written material. | Develop advertising campaigns for a wide range of clients, working with an advertising agency's creative director and art director to determine the best way to present advertising information. | Discuss with the client the product, advertising themes and methods, and any changes that should be made in advertising copy. | Edit or rewrite existing written material as necessary, and submit written material for approval by supervisor, editor, or publisher. | Follow appropriate procedures to get copyrights for completed work. | Invent names for products and write the slogans that appear on packaging, brochures and other promotional material. | Plan project arrangements or outlines, and organize material accordingly. | Prepare works in appropriate format for publication, and send them to publishers or producers. | Present drafts and ideas to clients. | Review advertising trends, consumer surveys, and other data regarding marketing of goods and services to determine the best way to promote products. | Revise written material to meet personal standards and to satisfy needs of clients, publishers, directors, or producers. | Vary language and tone of messages based on product and medium. | Work with staff to develop script, story, or advertising concepts. | Write advertising material for use by publication, broadcast, or internet media to promote the sale of goods and services. | Write articles, bulletins, sales letters, speeches, and other related informative, marketing and promotional material. | Write fiction or nonfiction prose, such as short stories, novels, biographies, articles, descriptive or critical analyses, and essays. | Write to customers in their terms and on their level so that the script, story, or advertisement message is more readily received.</t>
+  </si>
+  <si>
+    <t>Corporate Trainer | Driving Instructor | Flight Instructor | Instructor | Language Instructor | Music Teacher | Private Tutor | Test Preparation Instructor | Training Instructor | Workshop Facilitator</t>
+  </si>
+  <si>
+    <t>Learning management system LMS | Blackboard software | Microsoft PowerPoint | Microsoft Word | Microsoft Excel | Email software | Google Docs | Web browser software | Microsoft Outlook | Database software | Graphic presentation software | Microsoft Office software</t>
+  </si>
+  <si>
+    <t>Speaking | Active Listening | Reading Comprehension | Critical Thinking | Learning Strategies | Writing | Active Learning | Monitoring</t>
+  </si>
+  <si>
+    <t>Education and Training | English Language | Customer and Personal Service | Communications and Media | Psychology | Computers and Electronics | Administration and Management</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Written Comprehension | Oral Expression | Written Expression | Deductive Reasoning | Inductive Reasoning | Information Ordering | Problem Sensitivity | Near Vision | Speech Clarity | Speech Recognition | Category Flexibility | Fluency of Ideas | Originality | Selective Attention | Time Sharing | Visualization | Memorization</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Public Speaking | Contact With Others | Indoors, Environmentally Controlled | Deal With External Customers or the Public in General | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Work With or Contribute to a Work Group or Team | E-Mail | Telephone Conversations | Spend Time Standing | Time Pressure | Written Letters and Memos | Impact of Decisions on Co-workers or Company Results | Coordinate or Lead Others in Accomplishing Work Activities | Conflict Situations | Frequency of Decision Making</t>
+  </si>
+  <si>
+    <t>Self-Enrichment Teachers | Tutors | Substitute Teachers, Short-Term | Adult Basic Education, Adult Secondary Education, and English as a Second Language Instructors | Career/Technical Education Teachers, Secondary School | Career/Technical Education Teachers, Middle School | Career/Technical Education Teachers, Postsecondary | Training and Development Specialists | Training and Development Managers | Instructional Coordinators | Postsecondary Teachers, All Other | Elementary School Teachers, Except Special Education | Secondary School Teachers, Except Special and Career/Technical Education | Farm and Home Management Educators | Health Education Specialists | Educational, Guidance, and Career Counselors and Advisors | Coaches and Scouts | Recreation and Fitness Studies Teachers, Postsecondary | Education Administrators, All Other | Teaching Assistants, All Other</t>
+  </si>
+  <si>
+    <t>Instruct students in subjects and settings not classified separately. | Plan lessons, demonstrations, and practice activities appropriate to learner level. | Deliver instruction through lectures, demonstrations, and hands-on practice. | Evaluate learner performance and provide corrective feedback. | Prepare instructional materials, handouts, and practice exercises. | Administer tests and certify completion of instructional requirements. | Adapt teaching methods to accommodate different learning styles and abilities. | Maintain records of attendance, progress, and certification. | Ensure instructional areas and equipment are safe and properly maintained. | Advise learners on further study, practice routines, and career options. | Schedule classes, sessions, and use of instructional facilities. | Keep current with developments and standards in the subject taught. | Enforce safety rules and regulatory requirements during instruction. | Promote programs and recruit new students through outreach activities.</t>
+  </si>
+  <si>
+    <t>Classroom Aide | Educational Aide | Instructional Aide | Instructional Assistant | Learning Support Assistant | Paraeducator | Paraprofessional | Student Support Assistant | Teacher Aide | Teaching Assistant</t>
+  </si>
+  <si>
+    <t>Active Listening | Speaking | Reading Comprehension | Critical Thinking | Monitoring | Writing</t>
+  </si>
+  <si>
+    <t>Education and Training | English Language | Customer and Personal Service | Psychology | Computers and Electronics | Mathematics</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Speech Clarity | Speech Recognition | Near Vision | Problem Sensitivity | Information Ordering | Deductive Reasoning | Inductive Reasoning | Written Comprehension | Selective Attention | Category Flexibility | Time Sharing | Finger Dexterity | Manual Dexterity | Far Vision | Memorization | Fluency of Ideas</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Public Speaking | Contact With Others | Indoors, Environmentally Controlled | Deal With External Customers or the Public in General | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Work With or Contribute to a Work Group or Team | E-Mail | Telephone Conversations | Spend Time Standing | Time Pressure | Written Letters and Memos | Impact of Decisions on Co-workers or Company Results | Coordinate or Lead Others in Accomplishing Work Activities | Conflict Situations | Frequency of Decision Making | Physical Proximity | Importance of Repeating Same Tasks</t>
+  </si>
+  <si>
+    <t>Teaching Assistants, Preschool, Elementary, Middle, and Secondary School, Except Special Education | Teaching Assistants, Special Education | Teaching Assistants, Postsecondary | Tutors | Substitute Teachers, Short-Term | Self-Enrichment Teachers | Elementary School Teachers, Except Special Education | Preschool Teachers, Except Special Education | Kindergarten Teachers, Except Special Education | Middle School Teachers, Except Special and Career/Technical Education | Special Education Teachers, Elementary School | Special Education Teachers, All Other | Library Technicians | Librarians and Media Collections Specialists | Childcare Workers | Social and Human Service Assistants | Educational, Guidance, and Career Counselors and Advisors | Instructional Coordinators | Teachers and Instructors, All Other | Educational Instruction and Library Workers, All Other</t>
+  </si>
+  <si>
+    <t>Assist teachers and instructors in settings not classified separately. | Reinforce lessons by reviewing material with students individually or in small groups. | Supervise students in classrooms, laboratories, hallways, and on field trips. | Prepare instructional materials, equipment, and classroom displays. | Assist students with assignments, practice exercises, and use of learning technology. | Grade objective assignments and record scores in grade books or systems. | Take attendance and maintain records of student participation. | Assist students with physical, behavioral, or communication needs. | Set up and clean laboratory or activity areas before and after use. | Operate instructional equipment and audiovisual devices. | Communicate student progress and concerns to the supervising teacher. | Enforce classroom rules, safety procedures, and school policies. | Distribute and collect assignments, tests, and instructional supplies. | Assist with clerical tasks such as duplicating materials and preparing files.</t>
+  </si>
+  <si>
+    <t>Education Program Assistant | Education Specialist | Educational Support Worker | Learning Center Coordinator | Library Assistant | Media Center Assistant | Program Assistant | Resource Center Coordinator | Student Services Specialist | Testing Coordinator</t>
+  </si>
+  <si>
+    <t>Education and Training | English Language | Customer and Personal Service | Computers and Electronics | Administration and Management | Communications and Media</t>
+  </si>
+  <si>
+    <t>E-Mail | Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Indoors, Environmentally Controlled | Spend Time Sitting | Contact With Others | Work With or Contribute to a Work Group or Team | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Importance of Being Exact or Accurate | Time Pressure | Written Letters and Memos | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | Deal With External Customers or the Public in General | Spend Time Standing | Importance of Repeating Same Tasks</t>
+  </si>
+  <si>
+    <t>Library Technicians | Librarians and Media Collections Specialists | Archivists | Curators | Museum Technicians and Conservators | Instructional Coordinators | Teaching Assistants, All Other | Teaching Assistants, Postsecondary | Tutors | Self-Enrichment Teachers | Substitute Teachers, Short-Term | Teachers and Instructors, All Other | Education Administrators, All Other | Education Administrators, Postsecondary | Educational, Guidance, and Career Counselors and Advisors | Training and Development Specialists | Document Management Specialists | Office Clerks, General | Information and Record Clerks, All Other | Social and Human Service Assistants</t>
+  </si>
+  <si>
+    <t>Perform educational instruction and library support duties not classified separately. | Assist patrons and students in locating information, materials, and resources. | Organize, catalog, shelve, and maintain collections and instructional materials. | Coordinate scheduling of classrooms, resource centers, and equipment. | Administer standardized tests and maintain testing security procedures. | Prepare instructional and promotional materials, displays, and guides. | Operate and troubleshoot audiovisual, computer, and reproduction equipment. | Maintain circulation, attendance, and program participation records. | Process new acquisitions, repairs, and inventory of materials. | Provide orientation and training on use of facilities and resources. | Support program planning, events, and outreach activities. | Respond to inquiries from students, staff, and the public. | Compile statistics and prepare routine reports on services provided. | Order supplies and monitor budgets for assigned program areas.</t>
+  </si>
+  <si>
+    <t>Artist | Ceramic Artist | Digital Artist | Glass Artist | Illustrator | Mosaic Artist | Muralist | Printmaker | Sculptor | Textile Artist</t>
+  </si>
+  <si>
+    <t>Adobe Photoshop | Adobe Illustrator | Adobe InDesign | Adobe Acrobat | Graphics software | Microsoft Word | Microsoft Excel | Email software | Web browser software | Microsoft PowerPoint | Graphics editing software | Microsoft Office software</t>
+  </si>
+  <si>
+    <t>Fine Arts | Design | English Language | Communications and Media | Computers and Electronics | Sales and Marketing | History and Archeology | Administration and Management</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Speech Clarity | Speech Recognition | Near Vision | Problem Sensitivity | Information Ordering | Deductive Reasoning | Inductive Reasoning | Written Comprehension | Selective Attention | Category Flexibility | Time Sharing | Finger Dexterity | Manual Dexterity | Far Vision | Memorization | Fluency of Ideas | Originality | Visualization | Arm-Hand Steadiness | Visual Color Discrimination</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | E-Mail | Telephone Conversations | Indoors, Environmentally Controlled | Contact With Others | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Time Pressure | Level of Competition | Work With or Contribute to a Work Group or Team | Spend Time Sitting | Importance of Being Exact or Accurate | Deal With External Customers or the Public in General | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Frequency of Decision Making</t>
+  </si>
+  <si>
+    <t>Fine Artists, Including Painters, Sculptors, and Illustrators | Craft Artists | Special Effects Artists and Animators | Art Directors | Graphic Designers | Commercial and Industrial Designers | Fashion Designers | Interior Designers | Set and Exhibit Designers | Floral Designers | Merchandise Displayers and Window Trimmers | Designers, All Other | Photographers | Film and Video Editors | Camera Operators, Television, Video, and Film | Art, Drama, and Music Teachers, Postsecondary | Museum Technicians and Conservators | Curators | Self-Enrichment Teachers | Producers and Directors</t>
+  </si>
+  <si>
+    <t>Create original artworks in media and specialties not classified separately. | Develop concepts, sketches, and prototypes for artistic works. | Select and prepare materials, tools, and techniques appropriate to the medium. | Execute finished works using hand and digital methods. | Confer with clients, galleries, and agents about commissions and requirements. | Estimate materials, time, and costs for commissioned projects. | Photograph and document completed works for portfolios and catalogs. | Market and sell works through exhibitions, galleries, and online channels. | Maintain studio space, equipment, and material inventories. | Frame, mount, package, and ship artworks to clients and venues. | Study art history, trends, and techniques to develop artistic practice. | Prepare proposals and applications for grants, residencies, and public commissions. | Teach workshops and demonstrate techniques to students and the public. | Restore, conserve, or reproduce existing works when commissioned.</t>
+  </si>
+  <si>
+    <t>Design Consultant | Designer | Environmental Designer | Exhibit Designer | Jewelry Designer | Lighting Designer | Package Designer | Product Designer | Textile Designer | Toy Designer</t>
+  </si>
+  <si>
+    <t>Adobe Photoshop | Adobe Illustrator | Adobe InDesign | Adobe Acrobat | Graphics software | Microsoft Word | Microsoft Excel | Email software | Web browser software | Microsoft PowerPoint | Graphics editing software | Microsoft Office software | Autodesk AutoCAD | Three-dimensional 3D computer aided design CAD software</t>
+  </si>
+  <si>
+    <t>Reading Comprehension | Critical Thinking | Active Listening | Speaking | Writing | Monitoring | Active Learning | Learning Strategies</t>
+  </si>
+  <si>
+    <t>Design | Fine Arts | English Language | Computers and Electronics | Sales and Marketing | Production and Processing | Communications and Media | Engineering and Technology | Administration and Management</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Written Comprehension | Oral Expression | Written Expression | Deductive Reasoning | Inductive Reasoning | Information Ordering | Problem Sensitivity | Near Vision | Speech Clarity | Speech Recognition | Category Flexibility | Fluency of Ideas | Originality | Selective Attention | Time Sharing | Visualization | Memorization | Visual Color Discrimination | Finger Dexterity</t>
+  </si>
+  <si>
+    <t>Commercial and Industrial Designers | Graphic Designers | Interior Designers | Fashion Designers | Set and Exhibit Designers | Floral Designers | Merchandise Displayers and Window Trimmers | Art Directors | Special Effects Artists and Animators | Fine Artists, Including Painters, Sculptors, and Illustrators | Craft Artists | Artists and Related Workers, All Other | Web and Digital Interface Designers | Architects, Except Landscape and Naval | Landscape Architects | Art, Drama, and Music Teachers, Postsecondary | Mechanical Drafters | Video Game Designers | Photographers | Producers and Directors</t>
+  </si>
+  <si>
+    <t>Design products, environments, and displays in specialties not classified separately. | Consult with clients to determine design requirements, budgets, and timelines. | Research materials, methods, market trends, and user needs. | Prepare concept sketches, renderings, models, and technical drawings. | Select colors, materials, finishes, and components for designs. | Build prototypes and mock-ups to evaluate appearance and function. | Present design proposals to clients and revise based on feedback. | Coordinate with manufacturers, fabricators, and suppliers during production. | Prepare specifications, cost estimates, and production documentation. | Inspect completed work to verify conformance to design intent and quality standards. | Ensure designs comply with safety, accessibility, and regulatory requirements. | Maintain design files, material samples, and supplier records. | Track project schedules and budgets through completion. | Develop portfolios and promotional materials to attract clients.</t>
+  </si>
+  <si>
+    <t>Club DJ | Deejay | Disc Jockey | DJ | Event DJ | Mobile DJ | Party DJ | Turntablist | Wedding DJ | Nightclub DJ</t>
+  </si>
+  <si>
+    <t>Fine Arts | Customer and Personal Service | Communications and Media | English Language | Computers and Electronics | Sales and Marketing | Telecommunications</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Speech Clarity | Speech Recognition | Near Vision | Problem Sensitivity | Information Ordering | Deductive Reasoning | Inductive Reasoning | Written Comprehension | Selective Attention | Category Flexibility | Time Sharing | Finger Dexterity | Manual Dexterity | Far Vision | Memorization | Fluency of Ideas | Auditory Attention | Originality | Hearing Sensitivity | Arm-Hand Steadiness</t>
+  </si>
+  <si>
+    <t>Contact With Others | Deal With External Customers or the Public in General | Face-to-Face Discussions with Individuals and Within Teams | Physical Proximity | Spend Time Standing | Spend Time Walking or Running | Work With or Contribute to a Work Group or Team | Telephone Conversations | Indoors, Environmentally Controlled | Importance of Repeating Same Tasks | Time Pressure | Dealing With Unpleasant, Angry, or Discourteous People | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Frequency of Decision Making | Freedom to Make Decisions | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Level of Competition | Public Speaking | E-Mail</t>
+  </si>
+  <si>
+    <t>Circus Performer | Comedian | Entertainer | Magician | Performer | Puppeteer | Street Performer | Stunt Performer | Variety Artist | Voice Actor</t>
+  </si>
+  <si>
+    <t>Adobe Photoshop | Adobe Illustrator | Adobe InDesign | Adobe Acrobat | Graphics software | Microsoft Word | Microsoft Excel | Email software | Web browser software | Microsoft PowerPoint | Graphics editing software | Microsoft Office software | Scheduling software</t>
+  </si>
+  <si>
+    <t>Fine Arts | Communications and Media | English Language | Customer and Personal Service | Sales and Marketing | Education and Training | Psychology</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Speech Clarity | Speech Recognition | Near Vision | Problem Sensitivity | Information Ordering | Deductive Reasoning | Inductive Reasoning | Written Comprehension | Selective Attention | Category Flexibility | Time Sharing | Finger Dexterity | Manual Dexterity | Far Vision | Memorization | Fluency of Ideas | Originality | Gross Body Coordination | Stamina | Gross Body Equilibrium</t>
+  </si>
+  <si>
+    <t>Contact With Others | Deal With External Customers or the Public in General | Face-to-Face Discussions with Individuals and Within Teams | Physical Proximity | Spend Time Standing | Spend Time Walking or Running | Work With or Contribute to a Work Group or Team | Telephone Conversations | Indoors, Environmentally Controlled | Importance of Repeating Same Tasks | Time Pressure | Dealing With Unpleasant, Angry, or Discourteous People | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Frequency of Decision Making | Freedom to Make Decisions | Public Speaking | Level of Competition</t>
+  </si>
+  <si>
+    <t>Actors | Dancers | Choreographers | Musicians and Singers | Music Directors and Composers | Disc Jockeys, Except Radio | Athletes and Sports Competitors | Coaches and Scouts | Umpires, Referees, and Other Sports Officials | Producers and Directors | Talent Directors | Media Programming Directors | Broadcast Announcers and Radio Disc Jockeys | Art, Drama, and Music Teachers, Postsecondary | Self-Enrichment Teachers | Recreation Workers | Special Effects Artists and Animators | Set and Exhibit Designers | Agents and Business Managers of Artists, Performers, and Athletes | Media Technical Directors/Managers</t>
+  </si>
+  <si>
+    <t>Perform entertainment and related work in specialties not classified separately. | Develop, rehearse, and refine acts, routines, and performance material. | Perform before live audiences, cameras, or microphones. | Study scripts, music, and choreography to prepare for performances. | Audition for roles, engagements, and productions. | Coordinate with directors, producers, and technical crews during productions. | Maintain physical conditioning and technical skills through regular practice. | Select and maintain costumes, props, instruments, and equipment. | Travel to venues and adapt performances to different spaces and audiences. | Promote performances through media appearances and social channels. | Negotiate engagements, fees, and contracts with agents and venues. | Follow safety procedures for stunts, aerial work, and specialized effects. | Teach workshops and coach less experienced performers. | Maintain business records for bookings, income, and expenses.</t>
   </si>
 </sst>
 </file>
@@ -1977,8 +2112,32 @@
       <c r="B5" t="s">
         <v>45</v>
       </c>
+      <c r="C5" t="s">
+        <v>495</v>
+      </c>
+      <c r="D5" t="s">
+        <v>496</v>
+      </c>
+      <c r="E5" t="s">
+        <v>497</v>
+      </c>
+      <c r="F5" t="s">
+        <v>498</v>
+      </c>
+      <c r="G5" t="s">
+        <v>499</v>
+      </c>
+      <c r="H5" t="s">
+        <v>500</v>
+      </c>
+      <c r="I5" t="s">
+        <v>501</v>
+      </c>
       <c r="J5" t="s">
         <v>46</v>
+      </c>
+      <c r="K5" t="s">
+        <v>502</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
@@ -2338,8 +2497,32 @@
       <c r="B16" t="s">
         <v>158</v>
       </c>
+      <c r="C16" t="s">
+        <v>503</v>
+      </c>
+      <c r="D16" t="s">
+        <v>496</v>
+      </c>
+      <c r="E16" t="s">
+        <v>504</v>
+      </c>
+      <c r="F16" t="s">
+        <v>505</v>
+      </c>
+      <c r="G16" t="s">
+        <v>506</v>
+      </c>
+      <c r="H16" t="s">
+        <v>507</v>
+      </c>
+      <c r="I16" t="s">
+        <v>508</v>
+      </c>
       <c r="J16" t="s">
         <v>159</v>
+      </c>
+      <c r="K16" t="s">
+        <v>509</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
@@ -2349,8 +2532,32 @@
       <c r="B17" t="s">
         <v>161</v>
       </c>
+      <c r="C17" t="s">
+        <v>510</v>
+      </c>
+      <c r="D17" t="s">
+        <v>496</v>
+      </c>
+      <c r="E17" t="s">
+        <v>504</v>
+      </c>
+      <c r="F17" t="s">
+        <v>511</v>
+      </c>
+      <c r="G17" t="s">
+        <v>506</v>
+      </c>
+      <c r="H17" t="s">
+        <v>512</v>
+      </c>
+      <c r="I17" t="s">
+        <v>513</v>
+      </c>
       <c r="J17" t="s">
         <v>162</v>
+      </c>
+      <c r="K17" t="s">
+        <v>514</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
@@ -2500,8 +2707,32 @@
       <c r="B22" t="s">
         <v>208</v>
       </c>
+      <c r="C22" t="s">
+        <v>515</v>
+      </c>
+      <c r="D22" t="s">
+        <v>516</v>
+      </c>
+      <c r="E22" t="s">
+        <v>504</v>
+      </c>
+      <c r="F22" t="s">
+        <v>517</v>
+      </c>
+      <c r="G22" t="s">
+        <v>518</v>
+      </c>
+      <c r="H22" t="s">
+        <v>519</v>
+      </c>
+      <c r="I22" t="s">
+        <v>520</v>
+      </c>
       <c r="J22" t="s">
         <v>209</v>
+      </c>
+      <c r="K22" t="s">
+        <v>521</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
@@ -2756,8 +2987,32 @@
       <c r="B30" t="s">
         <v>288</v>
       </c>
+      <c r="C30" t="s">
+        <v>522</v>
+      </c>
+      <c r="D30" t="s">
+        <v>523</v>
+      </c>
+      <c r="E30" t="s">
+        <v>524</v>
+      </c>
+      <c r="F30" t="s">
+        <v>525</v>
+      </c>
+      <c r="G30" t="s">
+        <v>526</v>
+      </c>
+      <c r="H30" t="s">
+        <v>519</v>
+      </c>
+      <c r="I30" t="s">
+        <v>527</v>
+      </c>
       <c r="J30" t="s">
         <v>289</v>
+      </c>
+      <c r="K30" t="s">
+        <v>528</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
@@ -3187,8 +3442,23 @@
       <c r="B43" t="s">
         <v>422</v>
       </c>
+      <c r="C43" t="s">
+        <v>529</v>
+      </c>
       <c r="D43" t="s">
         <v>423</v>
+      </c>
+      <c r="E43" t="s">
+        <v>504</v>
+      </c>
+      <c r="F43" t="s">
+        <v>530</v>
+      </c>
+      <c r="G43" t="s">
+        <v>531</v>
+      </c>
+      <c r="H43" t="s">
+        <v>532</v>
       </c>
       <c r="I43" t="s">
         <v>424</v>
@@ -3207,8 +3477,32 @@
       <c r="B44" t="s">
         <v>428</v>
       </c>
+      <c r="C44" t="s">
+        <v>533</v>
+      </c>
+      <c r="D44" t="s">
+        <v>534</v>
+      </c>
+      <c r="E44" t="s">
+        <v>504</v>
+      </c>
+      <c r="F44" t="s">
+        <v>535</v>
+      </c>
+      <c r="G44" t="s">
+        <v>536</v>
+      </c>
+      <c r="H44" t="s">
+        <v>537</v>
+      </c>
+      <c r="I44" t="s">
+        <v>538</v>
+      </c>
       <c r="J44" t="s">
         <v>429</v>
+      </c>
+      <c r="K44" t="s">
+        <v>539</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.3">
